--- a/MiniTemplate/Datas/work.xlsx
+++ b/MiniTemplate/Datas/work.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F10087-EF61-464E-A35E-7D93FFBA961C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6444C527-642A-41B0-851B-3236B967445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="744" windowWidth="30696" windowHeight="16536" xr2:uid="{CCEF5422-2E44-42F0-BCF3-DCB33AE8BF91}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{CCEF5422-2E44-42F0-BCF3-DCB33AE8BF91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1121,10 +1121,10 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>20</v>
@@ -1153,10 +1153,10 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>30</v>
@@ -1185,7 +1185,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="I7">
         <v>12</v>
@@ -1226,7 +1226,7 @@
         <v>520</v>
       </c>
       <c r="I8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J8">
         <v>65</v>
@@ -1264,7 +1264,7 @@
         <v>680</v>
       </c>
       <c r="I9">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J9">
         <v>90</v>
@@ -1299,10 +1299,10 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>20</v>
@@ -1340,7 +1340,7 @@
         <v>450</v>
       </c>
       <c r="I11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>30</v>
@@ -1378,7 +1378,7 @@
         <v>700</v>
       </c>
       <c r="I12">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J12">
         <v>45</v>
@@ -1416,7 +1416,7 @@
         <v>1050</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J13">
         <v>65</v>
@@ -1454,7 +1454,7 @@
         <v>1600</v>
       </c>
       <c r="I14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J14">
         <v>90</v>
@@ -1489,10 +1489,10 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>20</v>
@@ -1527,10 +1527,10 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="I16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>30</v>
@@ -1568,7 +1568,7 @@
         <v>850</v>
       </c>
       <c r="I17">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J17">
         <v>45</v>
@@ -1606,7 +1606,7 @@
         <v>1350</v>
       </c>
       <c r="I18">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J18">
         <v>65</v>
@@ -1644,7 +1644,7 @@
         <v>2200</v>
       </c>
       <c r="I19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J19">
         <v>90</v>
@@ -1679,10 +1679,10 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>20</v>
@@ -1872,7 +1872,7 @@
         <v>280</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>20</v>
@@ -1910,7 +1910,7 @@
         <v>430</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>30</v>
@@ -1948,7 +1948,7 @@
         <v>680</v>
       </c>
       <c r="I27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>45</v>
@@ -1983,10 +1983,10 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="I28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28">
         <v>65</v>
@@ -2021,10 +2021,10 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>1600</v>
+        <v>1750</v>
       </c>
       <c r="I29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J29">
         <v>90</v>

--- a/MiniTemplate/Datas/work.xlsx
+++ b/MiniTemplate/Datas/work.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6444C527-642A-41B0-851B-3236B967445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30BE24C4-2BDF-479B-8600-683AC939156E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{CCEF5422-2E44-42F0-BCF3-DCB33AE8BF91}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CCEF5422-2E44-42F0-BCF3-DCB33AE8BF91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -908,24 +908,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD355D9D-C98C-47AD-A1A7-799954E007DF}">
   <dimension ref="A1:N34"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" customWidth="1"/>
-    <col min="5" max="5" width="54.6640625" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" customWidth="1"/>
-    <col min="7" max="7" width="21.88671875" customWidth="1"/>
-    <col min="8" max="9" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.109375" customWidth="1"/>
-    <col min="11" max="11" width="13.109375" customWidth="1"/>
-    <col min="12" max="12" width="26.44140625" customWidth="1"/>
-    <col min="13" max="13" width="25.6640625" customWidth="1"/>
-    <col min="14" max="14" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.75" customWidth="1"/>
+    <col min="5" max="5" width="54.625" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="7" max="7" width="21.875" customWidth="1"/>
+    <col min="8" max="9" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.125" customWidth="1"/>
+    <col min="11" max="11" width="13.125" customWidth="1"/>
+    <col min="12" max="12" width="26.5" customWidth="1"/>
+    <col min="13" max="13" width="25.625" customWidth="1"/>
+    <col min="14" max="14" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -969,7 +969,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>10001</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>10002</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>10003</v>
       </c>
@@ -1178,8 +1178,8 @@
       <c r="E7" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="2">
-        <v>1000</v>
+      <c r="F7">
+        <v>4000</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -1203,7 +1203,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>10004</v>
       </c>
@@ -1216,8 +1216,8 @@
       <c r="E8" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="2">
-        <v>1001</v>
+      <c r="F8">
+        <v>4001</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -1241,7 +1241,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>10005</v>
       </c>
@@ -1254,8 +1254,8 @@
       <c r="E9" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="2">
-        <v>1001</v>
+      <c r="F9">
+        <v>4002</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -1279,7 +1279,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>10006</v>
       </c>
@@ -1292,8 +1292,8 @@
       <c r="E10" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="2">
-        <v>1000</v>
+      <c r="F10">
+        <v>4003</v>
       </c>
       <c r="G10">
         <v>10</v>
@@ -1317,7 +1317,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>10007</v>
       </c>
@@ -1330,8 +1330,8 @@
       <c r="E11" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="2">
-        <v>1000</v>
+      <c r="F11">
+        <v>4004</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -1355,7 +1355,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>10008</v>
       </c>
@@ -1368,8 +1368,8 @@
       <c r="E12" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="2">
-        <v>1001</v>
+      <c r="F12">
+        <v>4005</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -1393,7 +1393,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>10009</v>
       </c>
@@ -1406,8 +1406,8 @@
       <c r="E13" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="2">
-        <v>1002</v>
+      <c r="F13">
+        <v>4006</v>
       </c>
       <c r="G13">
         <v>10</v>
@@ -1431,7 +1431,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>10010</v>
       </c>
@@ -1444,8 +1444,8 @@
       <c r="E14" t="s">
         <v>71</v>
       </c>
-      <c r="F14" s="2">
-        <v>1002</v>
+      <c r="F14">
+        <v>4007</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -1469,7 +1469,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>10011</v>
       </c>
@@ -1482,8 +1482,8 @@
       <c r="E15" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="2">
-        <v>1000</v>
+      <c r="F15">
+        <v>4008</v>
       </c>
       <c r="G15">
         <v>10</v>
@@ -1507,7 +1507,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>10012</v>
       </c>
@@ -1520,8 +1520,8 @@
       <c r="E16" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="2">
-        <v>1001</v>
+      <c r="F16">
+        <v>4009</v>
       </c>
       <c r="G16">
         <v>10</v>
@@ -1545,7 +1545,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>10013</v>
       </c>
@@ -1558,8 +1558,8 @@
       <c r="E17" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="2">
-        <v>1001</v>
+      <c r="F17">
+        <v>4010</v>
       </c>
       <c r="G17">
         <v>10</v>
@@ -1583,7 +1583,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>10014</v>
       </c>
@@ -1596,8 +1596,8 @@
       <c r="E18" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="2">
-        <v>1002</v>
+      <c r="F18">
+        <v>4011</v>
       </c>
       <c r="G18">
         <v>10</v>
@@ -1621,7 +1621,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>10015</v>
       </c>
@@ -1634,8 +1634,8 @@
       <c r="E19" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="2">
-        <v>1002</v>
+      <c r="F19">
+        <v>4012</v>
       </c>
       <c r="G19">
         <v>10</v>
@@ -1659,7 +1659,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>10016</v>
       </c>
@@ -1672,8 +1672,8 @@
       <c r="E20" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="2">
-        <v>1000</v>
+      <c r="F20">
+        <v>4013</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -1697,7 +1697,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>10017</v>
       </c>
@@ -1710,8 +1710,8 @@
       <c r="E21" t="s">
         <v>78</v>
       </c>
-      <c r="F21" s="2">
-        <v>1001</v>
+      <c r="F21">
+        <v>4014</v>
       </c>
       <c r="G21">
         <v>10</v>
@@ -1735,7 +1735,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>10018</v>
       </c>
@@ -1748,8 +1748,8 @@
       <c r="E22" t="s">
         <v>79</v>
       </c>
-      <c r="F22" s="2">
-        <v>1001</v>
+      <c r="F22">
+        <v>4015</v>
       </c>
       <c r="G22">
         <v>10</v>
@@ -1773,7 +1773,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>10019</v>
       </c>
@@ -1786,8 +1786,8 @@
       <c r="E23" t="s">
         <v>81</v>
       </c>
-      <c r="F23" s="2">
-        <v>1002</v>
+      <c r="F23">
+        <v>4016</v>
       </c>
       <c r="G23">
         <v>10</v>
@@ -1811,7 +1811,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>10020</v>
       </c>
@@ -1824,8 +1824,8 @@
       <c r="E24" t="s">
         <v>83</v>
       </c>
-      <c r="F24" s="2">
-        <v>1002</v>
+      <c r="F24">
+        <v>4017</v>
       </c>
       <c r="G24">
         <v>10</v>
@@ -1849,7 +1849,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>10021</v>
       </c>
@@ -1862,8 +1862,8 @@
       <c r="E25" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="2">
-        <v>1000</v>
+      <c r="F25">
+        <v>4018</v>
       </c>
       <c r="G25">
         <v>10</v>
@@ -1887,7 +1887,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>10022</v>
       </c>
@@ -1900,8 +1900,8 @@
       <c r="E26" t="s">
         <v>85</v>
       </c>
-      <c r="F26" s="2">
-        <v>1000</v>
+      <c r="F26">
+        <v>4019</v>
       </c>
       <c r="G26">
         <v>10</v>
@@ -1925,7 +1925,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>10023</v>
       </c>
@@ -1938,8 +1938,8 @@
       <c r="E27" t="s">
         <v>86</v>
       </c>
-      <c r="F27" s="2">
-        <v>1001</v>
+      <c r="F27">
+        <v>4020</v>
       </c>
       <c r="G27">
         <v>10</v>
@@ -1963,7 +1963,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>10024</v>
       </c>
@@ -1976,8 +1976,8 @@
       <c r="E28" t="s">
         <v>88</v>
       </c>
-      <c r="F28" s="2">
-        <v>1002</v>
+      <c r="F28">
+        <v>4021</v>
       </c>
       <c r="G28">
         <v>10</v>
@@ -2001,7 +2001,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>10025</v>
       </c>
@@ -2014,8 +2014,8 @@
       <c r="E29" t="s">
         <v>87</v>
       </c>
-      <c r="F29" s="2">
-        <v>1002</v>
+      <c r="F29">
+        <v>4022</v>
       </c>
       <c r="G29">
         <v>10</v>
@@ -2039,7 +2039,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>10026</v>
       </c>
@@ -2052,8 +2052,8 @@
       <c r="E30" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="2">
-        <v>1001</v>
+      <c r="F30">
+        <v>4023</v>
       </c>
       <c r="G30">
         <v>15</v>
@@ -2077,7 +2077,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>10027</v>
       </c>
@@ -2090,8 +2090,8 @@
       <c r="E31" t="s">
         <v>90</v>
       </c>
-      <c r="F31" s="2">
-        <v>1001</v>
+      <c r="F31">
+        <v>4024</v>
       </c>
       <c r="G31">
         <v>15</v>
@@ -2115,7 +2115,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>10028</v>
       </c>
@@ -2128,8 +2128,8 @@
       <c r="E32" t="s">
         <v>91</v>
       </c>
-      <c r="F32" s="2">
-        <v>1002</v>
+      <c r="F32">
+        <v>4025</v>
       </c>
       <c r="G32">
         <v>15</v>
@@ -2153,7 +2153,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B33">
         <v>10029</v>
       </c>
@@ -2166,8 +2166,8 @@
       <c r="E33" t="s">
         <v>92</v>
       </c>
-      <c r="F33" s="2">
-        <v>1002</v>
+      <c r="F33">
+        <v>4026</v>
       </c>
       <c r="G33">
         <v>15</v>
@@ -2191,7 +2191,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B34">
         <v>10030</v>
       </c>
@@ -2204,8 +2204,8 @@
       <c r="E34" t="s">
         <v>93</v>
       </c>
-      <c r="F34" s="2">
-        <v>1003</v>
+      <c r="F34">
+        <v>4027</v>
       </c>
       <c r="G34">
         <v>15</v>
